--- a/kiem_tra_du_lieu_nganh.xlsx
+++ b/kiem_tra_du_lieu_nganh.xlsx
@@ -21,9 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
+  <numFmts count="0"/>
   <fonts count="3">
     <font>
       <name val="Calibri"/>
@@ -83,10 +81,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -94,13 +95,13 @@
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
@@ -468,18 +469,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="43" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
-    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="13" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -505,31 +507,36 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>P/E Trung Vị</t>
+          <t>P/E Trung Vị Peers</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>P/B Trung Vị</t>
+          <t>P/B Trung Vị Peers</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ROE Bình Quân</t>
+          <t>ROE Bình Quân Peers</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Biên LN Ròng</t>
+          <t>Biên LN Ròng Peers</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Cỡ Mẫu Peers</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Trạng Thái</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -540,7 +547,7 @@
           <t>1750</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Sản xuất Thép &amp; Kim loại</t>
         </is>
@@ -550,25 +557,28 @@
           <t>RECOVERY</t>
         </is>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="E2" s="4" t="n">
         <v>14.85</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="4" t="n">
         <v>1.185</v>
       </c>
-      <c r="G2" s="4" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="H2" s="4" t="n">
+      <c r="G2" s="5" t="n">
+        <v>0.08425000000000001</v>
+      </c>
+      <c r="H2" s="5" t="n">
         <v>0.0275</v>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -579,7 +589,7 @@
           <t>9530</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
         <is>
           <t>Công nghệ thông tin &amp; Viễn thông</t>
         </is>
@@ -589,23 +599,28 @@
           <t>EXPANSION</t>
         </is>
       </c>
-      <c r="E3" s="3" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="F3" s="3" t="n">
+      <c r="E3" s="4" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="F3" s="4" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="G3" s="5" t="n">
+        <v>0.133</v>
+      </c>
+      <c r="H3" s="5" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I3" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>0.133</v>
-      </c>
-      <c r="H3" s="2" t="n"/>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="J3" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
@@ -616,7 +631,7 @@
           <t>8350</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại</t>
         </is>
@@ -626,23 +641,28 @@
           <t>RECOVERY</t>
         </is>
       </c>
-      <c r="E4" s="3" t="n">
-        <v>8.35</v>
-      </c>
-      <c r="F4" s="3" t="n">
+      <c r="E4" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="F4" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>0.1908</v>
       </c>
-      <c r="H4" s="2" t="n"/>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="H4" s="5" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
@@ -653,7 +673,7 @@
           <t>5370</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
         <is>
           <t>Bán lẻ tổng hợp &amp; Chuyên doanh</t>
         </is>
@@ -663,23 +683,28 @@
           <t>RECOVERY</t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
-        <v>16</v>
-      </c>
-      <c r="F5" s="3" t="n">
+      <c r="E5" s="4" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.211667</v>
+      </c>
+      <c r="H5" s="5" t="n">
+        <v>0.032333</v>
+      </c>
+      <c r="I5" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="G5" s="4" t="n">
-        <v>0.2117</v>
-      </c>
-      <c r="H5" s="2" t="n"/>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -690,7 +715,7 @@
           <t>8630</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Bất động sản dân cư &amp; Phát triển hạ tầng</t>
         </is>
@@ -700,23 +725,28 @@
           <t>RECOVERY</t>
         </is>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="F6" s="3" t="n">
+      <c r="F6" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="G6" s="4" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="H6" s="2" t="n"/>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="G6" s="5" t="n">
+        <v>0.059333</v>
+      </c>
+      <c r="H6" s="5" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>SSI</t>
@@ -727,7 +757,7 @@
           <t>8770</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Dịch vụ tài chính &amp; Chứng khoán</t>
         </is>
@@ -737,17 +767,22 @@
           <t>EXPANSION</t>
         </is>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="E7" s="4" t="n">
         <v>15.2</v>
       </c>
-      <c r="F7" s="3" t="n">
+      <c r="F7" s="4" t="n">
         <v>1.85</v>
       </c>
-      <c r="G7" s="4" t="n">
-        <v>0.1417</v>
-      </c>
-      <c r="H7" s="2" t="n"/>
-      <c r="I7" s="2" t="inlineStr">
+      <c r="G7" s="5" t="n">
+        <v>0.141667</v>
+      </c>
+      <c r="H7" s="5" t="n">
+        <v>0.358333</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
@@ -764,7 +799,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O22"/>
+  <dimension ref="A1:R22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -772,16 +807,19 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="47" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="12" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
-    <col width="15" customWidth="1" min="12" max="12"/>
-    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
     <col width="12" customWidth="1" min="14" max="14"/>
-    <col width="23" customWidth="1" min="15" max="15"/>
+    <col width="15" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="23" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -812,62 +850,77 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Ngày Định Giá</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Kỳ Tài Chính BCTC</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Phạm Vi Báo Cáo</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Vốn Hóa (VND)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Cơ Sở So Sánh</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>P/E</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>P/B</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>ROE</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>ROA</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Biên LN Ròng</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Biên LN Gộp</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>D/E</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Tăng Trưởng DT (YoY)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Sản xuất Thép &amp; Kim loại</t>
         </is>
@@ -877,7 +930,7 @@
           <t>NKG</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>CTCP Thép Nam Kim</t>
         </is>
@@ -887,46 +940,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I2" s="7" t="n">
         <v>5820000000000</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>Cùng phân khúc tôn mạ và thép cuộn xuất khẩu; biên lợi nhuận phụ thuộc lớn vào giá HRC đầu vào.</t>
         </is>
       </c>
-      <c r="H2" s="3" t="n">
+      <c r="K2" s="4" t="n">
         <v>12.8</v>
       </c>
-      <c r="I2" s="3" t="n">
+      <c r="L2" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="M2" s="5" t="n">
         <v>0.089</v>
       </c>
-      <c r="K2" s="4" t="n">
+      <c r="N2" s="5" t="n">
         <v>0.041</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="O2" s="5" t="n">
         <v>0.028</v>
       </c>
-      <c r="M2" s="4" t="n">
+      <c r="P2" s="5" t="n">
         <v>0.075</v>
       </c>
-      <c r="N2" s="3" t="n">
+      <c r="Q2" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="O2" s="4" t="n">
+      <c r="R2" s="5" t="n">
         <v>0.142</v>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>Sản xuất Thép &amp; Kim loại</t>
         </is>
@@ -936,7 +1004,7 @@
           <t>HSG</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>CTCP Tập đoàn Hoa Sen</t>
         </is>
@@ -946,46 +1014,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I3" s="7" t="n">
         <v>12450000000000</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>Doanh nghiệp chiếm thị phần tôn mạ số 1 Việt Nam (khoảng 28-30%); hệ thống phân phối bán lẻ Hoa Sen Home rộng khắp.</t>
         </is>
       </c>
-      <c r="H3" s="3" t="n">
+      <c r="K3" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="I3" s="3" t="n">
+      <c r="L3" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="M3" s="5" t="n">
         <v>0.098</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="N3" s="5" t="n">
         <v>0.048</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="O3" s="5" t="n">
         <v>0.032</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="P3" s="5" t="n">
         <v>0.112</v>
       </c>
-      <c r="N3" s="3" t="n">
+      <c r="Q3" s="4" t="n">
         <v>0.72</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="R3" s="5" t="n">
         <v>0.115</v>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>Sản xuất Thép &amp; Kim loại</t>
         </is>
@@ -995,7 +1078,7 @@
           <t>VGS</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>CTCP Ống thép Việt Đức</t>
         </is>
@@ -1005,46 +1088,61 @@
           <t>HNX</t>
         </is>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I4" s="7" t="n">
         <v>3120000000000</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>Chuyên về sản phẩm ống thép xây dựng và kết cấu thép miền Bắc; hưởng lợi lớn từ sóng giải ngân đầu tư công hạ tầng.</t>
         </is>
       </c>
-      <c r="H4" s="3" t="n">
+      <c r="K4" s="4" t="n">
         <v>15.2</v>
       </c>
-      <c r="I4" s="3" t="n">
+      <c r="L4" s="4" t="n">
         <v>1.48</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="M4" s="5" t="n">
         <v>0.115</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="N4" s="5" t="n">
         <v>0.052</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="O4" s="5" t="n">
         <v>0.038</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="P4" s="5" t="n">
         <v>0.089</v>
       </c>
-      <c r="N4" s="3" t="n">
+      <c r="Q4" s="4" t="n">
         <v>0.88</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="R4" s="5" t="n">
         <v>0.168</v>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
         <is>
           <t>Sản xuất Thép &amp; Kim loại</t>
         </is>
@@ -1054,7 +1152,7 @@
           <t>TVN</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D5" s="3" t="inlineStr">
         <is>
           <t>Tổng Công ty Thép Việt Nam - CTCP</t>
         </is>
@@ -1064,46 +1162,61 @@
           <t>UPCOM</t>
         </is>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I5" s="7" t="n">
         <v>6150000000000</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="J5" s="3" t="inlineStr">
         <is>
           <t>Tập đoàn quốc doanh sản xuất phôi thép và thép xây dựng truyền thống; năng lực công nghệ và biên lợi nhuận thấp hơn khối tư nhân.</t>
         </is>
       </c>
-      <c r="H5" s="3" t="n">
+      <c r="K5" s="4" t="n">
         <v>18.6</v>
       </c>
-      <c r="I5" s="3" t="n">
+      <c r="L5" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="M5" s="5" t="n">
         <v>0.035</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="N5" s="5" t="n">
         <v>0.014</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="O5" s="5" t="n">
         <v>0.012</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="P5" s="5" t="n">
         <v>0.045</v>
       </c>
-      <c r="N5" s="3" t="n">
+      <c r="Q5" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="R5" s="5" t="n">
         <v>0.062</v>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>Công nghệ thông tin &amp; Viễn thông</t>
         </is>
@@ -1113,7 +1226,7 @@
           <t>CMG</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>CTCP Tập đoàn Công nghệ CMC</t>
         </is>
@@ -1123,46 +1236,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I6" s="7" t="n">
         <v>8950000000000</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Đối thủ lớn thứ 2 tại Việt Nam trong mảng chuyển đổi số doanh nghiệp, viễn thông và hạ tầng trung tâm dữ liệu (Data Center).</t>
         </is>
       </c>
-      <c r="H6" s="3" t="n">
+      <c r="K6" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="I6" s="3" t="n">
+      <c r="L6" s="4" t="n">
         <v>3.85</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="M6" s="5" t="n">
         <v>0.165</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="N6" s="5" t="n">
         <v>0.078</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="O6" s="5" t="n">
         <v>0.082</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="P6" s="5" t="n">
         <v>0.215</v>
       </c>
-      <c r="N6" s="3" t="n">
+      <c r="Q6" s="4" t="n">
         <v>0.45</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="R6" s="5" t="n">
         <v>0.185</v>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Công nghệ thông tin &amp; Viễn thông</t>
         </is>
@@ -1172,7 +1300,7 @@
           <t>ELC</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>CTCP Công nghệ - Viễn thông Elcom</t>
         </is>
@@ -1182,46 +1310,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I7" s="7" t="n">
         <v>2150000000000</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>Tập trung chuyên sâu vào giải pháp giao thông thông minh (ITS), viễn thông và an ninh số; hưởng lợi từ các dự án cao tốc quốc gia.</t>
         </is>
       </c>
-      <c r="H7" s="3" t="n">
+      <c r="K7" s="4" t="n">
         <v>16.8</v>
       </c>
-      <c r="I7" s="3" t="n">
+      <c r="L7" s="4" t="n">
         <v>2.15</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="M7" s="5" t="n">
         <v>0.142</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="N7" s="5" t="n">
         <v>0.08500000000000001</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="O7" s="5" t="n">
         <v>0.095</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="P7" s="5" t="n">
         <v>0.285</v>
       </c>
-      <c r="N7" s="3" t="n">
+      <c r="Q7" s="4" t="n">
         <v>0.22</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="R7" s="5" t="n">
         <v>0.245</v>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>Công nghệ thông tin &amp; Viễn thông</t>
         </is>
@@ -1231,7 +1374,7 @@
           <t>ITD</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>CTCP Công nghệ Tiên Phong</t>
         </is>
@@ -1241,46 +1384,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I8" s="7" t="n">
         <v>680000000000</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="J8" s="3" t="inlineStr">
         <is>
           <t>Cung cấp giải pháp hạ tầng thông tin, tự động hóa và tích hợp hệ thống cho khối chính phủ và doanh nghiệp vừa.</t>
         </is>
       </c>
-      <c r="H8" s="3" t="n">
+      <c r="K8" s="4" t="n">
         <v>14.2</v>
       </c>
-      <c r="I8" s="3" t="n">
+      <c r="L8" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="M8" s="5" t="n">
         <v>0.092</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="N8" s="5" t="n">
         <v>0.045</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="O8" s="5" t="n">
         <v>0.042</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="P8" s="5" t="n">
         <v>0.185</v>
       </c>
-      <c r="N8" s="3" t="n">
+      <c r="Q8" s="4" t="n">
         <v>0.35</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="R8" s="5" t="n">
         <v>0.08500000000000001</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại</t>
         </is>
@@ -1290,7 +1448,7 @@
           <t>BID</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng TMCP Đầu tư và Phát triển Việt Nam</t>
         </is>
@@ -1300,44 +1458,63 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I9" s="7" t="n">
         <v>275000000000000</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Ngân hàng có quy mô tổng tài sản lớn nhất hệ thống; tập trung mạng lưới phục vụ các dự án trọng điểm quốc gia và doanh nghiệp lớn.</t>
-        </is>
-      </c>
-      <c r="H9" s="3" t="n">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Ngân hàng có quy mô tổng tài sản lớn nhất hệ thống; mạng lưới phục vụ các dự án hạ tầng quốc gia và doanh nghiệp lớn.</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="n">
         <v>11.8</v>
       </c>
-      <c r="I9" s="3" t="n">
+      <c r="L9" s="4" t="n">
         <v>1.95</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="M9" s="5" t="n">
         <v>0.178</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="N9" s="5" t="n">
         <v>0.012</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="O9" s="5" t="n">
         <v>0.312</v>
       </c>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="3" t="n">
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>N/A (Đặc thù)</t>
+        </is>
+      </c>
+      <c r="Q9" s="4" t="n">
         <v>14.5</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="R9" s="5" t="n">
         <v>0.135</v>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại</t>
         </is>
@@ -1347,7 +1524,7 @@
           <t>CTG</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng TMCP Công Thương Việt Nam</t>
         </is>
@@ -1357,44 +1534,63 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I10" s="7" t="n">
         <v>192000000000000</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Ngân hàng quốc doanh trụ cột trong khối Big 4, tăng trưởng mạnh ở phân khúc khách hàng FDI và bán lẻ tiêu dùng.</t>
-        </is>
-      </c>
-      <c r="H10" s="3" t="n">
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Ngân hàng quốc doanh trụ cột trong khối Big 4, tăng trưởng mạnh ở phân khúc khách hàng FDI và khách hàng doanh nghiệp.</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="n">
         <v>9.199999999999999</v>
       </c>
-      <c r="I10" s="3" t="n">
+      <c r="L10" s="4" t="n">
         <v>1.42</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="M10" s="5" t="n">
         <v>0.165</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="N10" s="5" t="n">
         <v>0.011</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="O10" s="5" t="n">
         <v>0.335</v>
       </c>
-      <c r="M10" s="2" t="n"/>
-      <c r="N10" s="3" t="n">
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>N/A (Đặc thù)</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="n">
         <v>13.8</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="R10" s="5" t="n">
         <v>0.142</v>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại</t>
         </is>
@@ -1404,7 +1600,7 @@
           <t>TCB</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng TMCP Kỹ Thương Việt Nam</t>
         </is>
@@ -1414,44 +1610,63 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I11" s="7" t="n">
         <v>122000000000000</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Ngân hàng thương mại cổ phần tư nhân dẫn đầu về tỷ lệ tiền gửi không kỳ hạn CASA (&gt;40%) và hệ số an toàn vốn CAR chuẩn Basel II/III.</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="n">
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Ngân hàng thương mại cổ phần tư nhân dẫn đầu về tỷ lệ tiền gửi không kỳ hạn CASA (&gt;38%) và hệ số an toàn vốn CAR cao.</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="n">
         <v>7.5</v>
       </c>
-      <c r="I11" s="3" t="n">
+      <c r="L11" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="M11" s="5" t="n">
         <v>0.168</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="N11" s="5" t="n">
         <v>0.024</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="O11" s="5" t="n">
         <v>0.425</v>
       </c>
-      <c r="M11" s="2" t="n"/>
-      <c r="N11" s="3" t="n">
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>N/A (Đặc thù)</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="R11" s="5" t="n">
         <v>0.185</v>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại</t>
         </is>
@@ -1461,7 +1676,7 @@
           <t>MBB</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng TMCP Quân Đội</t>
         </is>
@@ -1471,44 +1686,63 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I12" s="7" t="n">
         <v>118000000000000</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Ngân hàng số hàng đầu với chi phí vốn thấp nhờ lượng CASA khách hàng cá nhân khổng lồ và hệ sinh thái tài chính đa năng (bảo hiểm, chứng khoán).</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="n">
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Ngân hàng số hàng đầu với chi phí vốn thấp nhờ lượng CASA khách hàng cá nhân dồi dào và hệ sinh thái tài chính đa năng.</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="n">
         <v>6.2</v>
       </c>
-      <c r="I12" s="3" t="n">
+      <c r="L12" s="4" t="n">
         <v>1.12</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="M12" s="5" t="n">
         <v>0.215</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="N12" s="5" t="n">
         <v>0.025</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="O12" s="5" t="n">
         <v>0.412</v>
       </c>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="3" t="n">
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>N/A (Đặc thù)</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="n">
         <v>7.5</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="R12" s="5" t="n">
         <v>0.162</v>
       </c>
     </row>
-    <row r="13" ht="20" customHeight="1">
+    <row r="13" ht="22" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng thương mại</t>
         </is>
@@ -1518,7 +1752,7 @@
           <t>ACB</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng TMCP Á Châu</t>
         </is>
@@ -1528,44 +1762,63 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I13" s="7" t="n">
         <v>105000000000000</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Mô hình quản trị rủi ro tín dụng thận trọng nhất khối tư nhân, danh mục cho vay phân tán tuyệt đối vào khách hàng cá nhân và SME sạch.</t>
-        </is>
-      </c>
-      <c r="H13" s="3" t="n">
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Mô hình quản trị rủi ro tín dụng thận trọng khối tư nhân, danh mục cho vay phân tán vào khách hàng cá nhân và SME lành mạnh.</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="n">
         <v>6.8</v>
       </c>
-      <c r="I13" s="3" t="n">
+      <c r="L13" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="M13" s="5" t="n">
         <v>0.228</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="N13" s="5" t="n">
         <v>0.023</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="O13" s="5" t="n">
         <v>0.435</v>
       </c>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="3" t="n">
+      <c r="P13" s="3" t="inlineStr">
+        <is>
+          <t>N/A (Đặc thù)</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="n">
         <v>8.199999999999999</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="R13" s="5" t="n">
         <v>0.128</v>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
+    <row r="14" ht="22" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>Bán lẻ tổng hợp &amp; Chuyên doanh</t>
         </is>
@@ -1575,7 +1828,7 @@
           <t>FRT</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>CTCP Bán lẻ Kỹ thuật số FPT</t>
         </is>
@@ -1585,46 +1838,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I14" s="7" t="n">
         <v>24500000000000</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Mô hình tăng trưởng đột phá với chuỗi nhà thuốc Long Châu dẫn đầu toàn quốc và FPT Shop tái cơ cấu.</t>
-        </is>
-      </c>
-      <c r="H14" s="3" t="n">
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Mô hình tăng trưởng bán lẻ dược phẩm qua chuỗi Long Châu dẫn đầu toàn quốc và chuỗi FPT Shop tái cơ cấu.</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="n">
         <v>32.5</v>
       </c>
-      <c r="I14" s="3" t="n">
+      <c r="L14" s="4" t="n">
         <v>7.2</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="M14" s="5" t="n">
         <v>0.225</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="N14" s="5" t="n">
         <v>0.045</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="O14" s="5" t="n">
         <v>0.018</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="P14" s="5" t="n">
         <v>0.215</v>
       </c>
-      <c r="N14" s="3" t="n">
+      <c r="Q14" s="4" t="n">
         <v>2.85</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="R14" s="5" t="n">
         <v>0.285</v>
       </c>
     </row>
-    <row r="15" ht="20" customHeight="1">
+    <row r="15" ht="22" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>Bán lẻ tổng hợp &amp; Chuyên doanh</t>
         </is>
@@ -1634,7 +1902,7 @@
           <t>DGW</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>CTCP Thế Giới Số</t>
         </is>
@@ -1644,46 +1912,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n">
         <v>9800000000000</v>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Nhà phân phối ủy quyền ICT, thiết bị văn phòng và hàng tiêu dùng nhanh (FMCG) cho các thương hiệu hàng đầu thế giới.</t>
-        </is>
-      </c>
-      <c r="H15" s="3" t="n">
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Nhà phân phối ủy quyền thiết bị ICT, điện máy và hàng tiêu dùng nhanh (FMCG) cho các thương hiệu quốc tế.</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="n">
         <v>16.2</v>
       </c>
-      <c r="I15" s="3" t="n">
+      <c r="L15" s="4" t="n">
         <v>2.85</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="M15" s="5" t="n">
         <v>0.175</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="N15" s="5" t="n">
         <v>0.068</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="O15" s="5" t="n">
         <v>0.024</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="P15" s="5" t="n">
         <v>0.082</v>
       </c>
-      <c r="N15" s="3" t="n">
+      <c r="Q15" s="4" t="n">
         <v>0.95</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="R15" s="5" t="n">
         <v>0.165</v>
       </c>
     </row>
-    <row r="16" ht="20" customHeight="1">
+    <row r="16" ht="22" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Bán lẻ tổng hợp &amp; Chuyên doanh</t>
         </is>
@@ -1693,7 +1976,7 @@
           <t>PNJ</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="3" t="inlineStr">
         <is>
           <t>CTCP Vàng bạc Đá quý Phú Nhuận</t>
         </is>
@@ -1703,46 +1986,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I16" s="7" t="n">
         <v>32000000000000</v>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>Bán lẻ trang sức và quà tặng cao cấp chiếm lĩnh thị phần áp đảo với biên lợi nhuận ròng vượt trội ngành tiêu dùng.</t>
         </is>
       </c>
-      <c r="H16" s="3" t="n">
+      <c r="K16" s="4" t="n">
         <v>15.8</v>
       </c>
-      <c r="I16" s="3" t="n">
+      <c r="L16" s="4" t="n">
         <v>3.12</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="M16" s="5" t="n">
         <v>0.235</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="N16" s="5" t="n">
         <v>0.145</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="O16" s="5" t="n">
         <v>0.055</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="P16" s="5" t="n">
         <v>0.185</v>
       </c>
-      <c r="N16" s="3" t="n">
+      <c r="Q16" s="4" t="n">
         <v>0.25</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="R16" s="5" t="n">
         <v>0.142</v>
       </c>
     </row>
-    <row r="17" ht="20" customHeight="1">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
         <is>
           <t>VHM</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>Bất động sản dân cư &amp; Phát triển hạ tầng</t>
         </is>
@@ -1752,7 +2050,7 @@
           <t>KDH</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>CTCP Đầu tư và Kinh doanh Nhà Khang Điền</t>
         </is>
@@ -1762,46 +2060,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I17" s="7" t="n">
         <v>31500000000000</v>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>Doanh nghiệp sở hữu quỹ đất sạch pháp lý hoàn chỉnh tại TP.HCM, cơ cấu tài chính lành mạnh, hợp tác cùng Keppel Land.</t>
         </is>
       </c>
-      <c r="H17" s="3" t="n">
+      <c r="K17" s="4" t="n">
         <v>24.5</v>
       </c>
-      <c r="I17" s="3" t="n">
+      <c r="L17" s="4" t="n">
         <v>1.75</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="M17" s="5" t="n">
         <v>0.075</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="N17" s="5" t="n">
         <v>0.042</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="O17" s="5" t="n">
         <v>0.285</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="P17" s="5" t="n">
         <v>0.485</v>
       </c>
-      <c r="N17" s="3" t="n">
+      <c r="Q17" s="4" t="n">
         <v>0.42</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="R17" s="5" t="n">
         <v>0.325</v>
       </c>
     </row>
-    <row r="18" ht="20" customHeight="1">
+    <row r="18" ht="22" customHeight="1">
       <c r="A18" s="2" t="inlineStr">
         <is>
           <t>VHM</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>Bất động sản dân cư &amp; Phát triển hạ tầng</t>
         </is>
@@ -1811,7 +2124,7 @@
           <t>NLG</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>CTCP Đầu tư Nam Long</t>
         </is>
@@ -1821,46 +2134,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I18" s="7" t="n">
         <v>18200000000000</v>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="J18" s="3" t="inlineStr">
         <is>
           <t>Dẫn đầu phân khúc nhà ở vừa túi tiền (Affordable housing) với chuỗi dự án Akari City, Mizuki Park, Waterpoint liên doanh đối tác Nhật Bản.</t>
         </is>
       </c>
-      <c r="H18" s="3" t="n">
+      <c r="K18" s="4" t="n">
         <v>22.8</v>
       </c>
-      <c r="I18" s="3" t="n">
+      <c r="L18" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="M18" s="5" t="n">
         <v>0.068</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="N18" s="5" t="n">
         <v>0.038</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="O18" s="5" t="n">
         <v>0.165</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="P18" s="5" t="n">
         <v>0.385</v>
       </c>
-      <c r="N18" s="3" t="n">
+      <c r="Q18" s="4" t="n">
         <v>0.48</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="R18" s="5" t="n">
         <v>0.185</v>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
+    <row r="19" ht="22" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
         <is>
           <t>VHM</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>Bất động sản dân cư &amp; Phát triển hạ tầng</t>
         </is>
@@ -1870,7 +2198,7 @@
           <t>DXG</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="3" t="inlineStr">
         <is>
           <t>CTCP Tập đoàn Đất Xanh</t>
         </is>
@@ -1880,46 +2208,61 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I19" s="7" t="n">
         <v>12400000000000</v>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="J19" s="3" t="inlineStr">
         <is>
           <t>Tập đoàn phát triển bất động sản và dịch vụ môi giới chiếm thị phần môi giới bán hàng lớn nhất miền Nam.</t>
         </is>
       </c>
-      <c r="H19" s="3" t="n">
+      <c r="K19" s="4" t="n">
         <v>35.2</v>
       </c>
-      <c r="I19" s="3" t="n">
+      <c r="L19" s="4" t="n">
         <v>1.15</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="M19" s="5" t="n">
         <v>0.035</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="N19" s="5" t="n">
         <v>0.015</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="O19" s="5" t="n">
         <v>0.045</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="P19" s="5" t="n">
         <v>0.425</v>
       </c>
-      <c r="N19" s="3" t="n">
+      <c r="Q19" s="4" t="n">
         <v>0.65</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="R19" s="5" t="n">
         <v>0.125</v>
       </c>
     </row>
-    <row r="20" ht="20" customHeight="1">
+    <row r="20" ht="22" customHeight="1">
       <c r="A20" s="2" t="inlineStr">
         <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>Dịch vụ tài chính &amp; Chứng khoán</t>
         </is>
@@ -1929,7 +2272,7 @@
           <t>VCI</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>CTCP Chứng khoán Vietcap</t>
         </is>
@@ -1939,44 +2282,63 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I20" s="7" t="n">
         <v>23500000000000</v>
       </c>
-      <c r="G20" s="2" t="inlineStr">
+      <c r="J20" s="3" t="inlineStr">
         <is>
           <t>Thế mạnh số 1 thị trường về mảng tư vấn ngân hàng đầu tư (IB), bảo lãnh phát hành và khách hàng tổ chức nước ngoài.</t>
         </is>
       </c>
-      <c r="H20" s="3" t="n">
+      <c r="K20" s="4" t="n">
         <v>16.5</v>
       </c>
-      <c r="I20" s="3" t="n">
+      <c r="L20" s="4" t="n">
         <v>2.15</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="M20" s="5" t="n">
         <v>0.155</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="N20" s="5" t="n">
         <v>0.065</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="O20" s="5" t="n">
         <v>0.385</v>
       </c>
-      <c r="M20" s="2" t="n"/>
-      <c r="N20" s="3" t="n">
+      <c r="P20" s="3" t="inlineStr">
+        <is>
+          <t>N/A (Đặc thù)</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="n">
         <v>1.25</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="R20" s="5" t="n">
         <v>0.285</v>
       </c>
     </row>
-    <row r="21" ht="20" customHeight="1">
+    <row r="21" ht="22" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
         <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Dịch vụ tài chính &amp; Chứng khoán</t>
         </is>
@@ -1986,7 +2348,7 @@
           <t>VND</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D21" s="3" t="inlineStr">
         <is>
           <t>CTCP Chứng khoán VNDIRECT</t>
         </is>
@@ -1996,44 +2358,63 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H21" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I21" s="7" t="n">
         <v>22800000000000</v>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="J21" s="3" t="inlineStr">
         <is>
           <t>Quy mô vốn điều lệ và lượng khách hàng cá nhân giao dịch thuộc top 3 toàn thị trường, mảng công nghệ số mạnh.</t>
         </is>
       </c>
-      <c r="H21" s="3" t="n">
+      <c r="K21" s="4" t="n">
         <v>13.8</v>
       </c>
-      <c r="I21" s="3" t="n">
+      <c r="L21" s="4" t="n">
         <v>1.35</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="M21" s="5" t="n">
         <v>0.125</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="N21" s="5" t="n">
         <v>0.048</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="O21" s="5" t="n">
         <v>0.325</v>
       </c>
-      <c r="M21" s="2" t="n"/>
-      <c r="N21" s="3" t="n">
+      <c r="P21" s="3" t="inlineStr">
+        <is>
+          <t>N/A (Đặc thù)</t>
+        </is>
+      </c>
+      <c r="Q21" s="4" t="n">
         <v>1.85</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="R21" s="5" t="n">
         <v>0.165</v>
       </c>
     </row>
-    <row r="22" ht="20" customHeight="1">
+    <row r="22" ht="22" customHeight="1">
       <c r="A22" s="2" t="inlineStr">
         <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Dịch vụ tài chính &amp; Chứng khoán</t>
         </is>
@@ -2043,7 +2424,7 @@
           <t>HCM</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="D22" s="3" t="inlineStr">
         <is>
           <t>CTCP Chứng khoán Thành phố Hồ Chí Minh (HSC)</t>
         </is>
@@ -2053,34 +2434,53 @@
           <t>HOSE</t>
         </is>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="H22" s="3" t="inlineStr">
+        <is>
+          <t>consolidated</t>
+        </is>
+      </c>
+      <c r="I22" s="7" t="n">
         <v>21200000000000</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>Cơ cấu tài chính an toàn tuyệt đối, thị phần môi giới top 3 và danh mục tự doanh thận trọng.</t>
-        </is>
-      </c>
-      <c r="H22" s="3" t="n">
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Cơ cấu tài chính an toàn, thị phần môi giới top 3 và danh mục tự doanh thận trọng.</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="n">
         <v>15.2</v>
       </c>
-      <c r="I22" s="3" t="n">
+      <c r="L22" s="4" t="n">
         <v>1.85</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="M22" s="5" t="n">
         <v>0.145</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="N22" s="5" t="n">
         <v>0.058</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="O22" s="5" t="n">
         <v>0.365</v>
       </c>
-      <c r="M22" s="2" t="n"/>
-      <c r="N22" s="3" t="n">
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>N/A (Đặc thù)</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="n">
         <v>1.45</v>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="R22" s="5" t="n">
         <v>0.225</v>
       </c>
     </row>
@@ -2095,19 +2495,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="38" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="52" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="11" max="11"/>
+    <col width="38" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -2153,16 +2555,26 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>Công Thức</t>
+          <t>Cỡ Mẫu</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Mã Nguồn</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>Phương Pháp &amp; Ghi Chú Tái Lập</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Công Thức ID</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Mã Nguồn Trích Dẫn</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -2173,20 +2585,20 @@
           <t>ind_pe_median</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>P/E trung vị ngành Thép</t>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>P/E trung vị nhóm so sánh (Peers Median P/E)</t>
         </is>
       </c>
       <c r="D2" s="6" t="n">
         <v>14.85</v>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
@@ -2201,18 +2613,26 @@
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="I2" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 4 peers: NKG (12.8), HSG (14.5), VGS (15.2), TVN (18.6) = (14.5 + 15.2) / 2 = 14.85x</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>median_peer_pe</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
+      <c r="L2" s="2" t="inlineStr">
         <is>
           <t>ind_src_vietstock_steel_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -2223,20 +2643,20 @@
           <t>ind_pb_median</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>P/B trung vị ngành Thép</t>
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>P/B trung vị nhóm so sánh (Peers Median P/B)</t>
         </is>
       </c>
       <c r="D3" s="6" t="n">
         <v>1.185</v>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
@@ -2251,18 +2671,26 @@
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I3" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 4 peers: TVN (0.65), NKG (1.12), HSG (1.25), VGS (1.48) = (1.12 + 1.25) / 2 = 1.185x</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>median_peer_pb</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="L3" s="2" t="inlineStr">
         <is>
           <t>ind_src_vietstock_steel_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="20" customHeight="1">
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -2273,20 +2701,20 @@
           <t>ind_roe_avg</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>ROE bình quân ngành Thép</t>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>ROE bình quân nhóm so sánh (Peers Mean ROE)</t>
         </is>
       </c>
       <c r="D4" s="6" t="n">
-        <v>0.08400000000000001</v>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+        <v>0.08425000000000001</v>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
@@ -2301,18 +2729,26 @@
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I4" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 4 peers: (0.089 + 0.098 + 0.115 + 0.035) / 4 = 0.08425</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>mean_peer_roe</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>ind_src_vietstock_steel_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -2323,20 +2759,20 @@
           <t>ind_net_margin_avg</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Biên lợi nhuận ròng bình quân ngành</t>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng bình quân nhóm so sánh</t>
         </is>
       </c>
       <c r="D5" s="6" t="n">
         <v>0.0275</v>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
@@ -2351,18 +2787,26 @@
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="I5" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 4 peers: (0.028 + 0.032 + 0.038 + 0.012) / 4 = 0.0275</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>mean_peer_net_margin</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>ind_src_vietstock_steel_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -2373,20 +2817,20 @@
           <t>ind_crude_steel_consumption_growth</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Tăng trưởng tiêu thụ thép toàn quốc 8T/2026 (YoY)</t>
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Tăng trưởng bán hàng thép xây dựng &amp; HRC toàn ngành 8T/2026 (YoY)</t>
         </is>
       </c>
       <c r="D6" s="6" t="n">
         <v>0.118</v>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F6" s="3" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
@@ -2403,16 +2847,26 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>Lũy kế sản lượng bán hàng 8 tháng 2026 so với cùng kỳ 2025 theo báo cáo VSA</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
           <t>vsa_yoy_sales_growth</t>
         </is>
       </c>
-      <c r="J6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>ind_src_vsa_report_2026</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -2423,7 +2877,7 @@
           <t>ind_iip_metal_growth</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Chỉ số IIP sản xuất kim loại 9 tháng 2026 (YoY)</t>
         </is>
@@ -2431,12 +2885,12 @@
       <c r="D7" s="6" t="n">
         <v>0.106</v>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>quarterly</t>
         </is>
@@ -2453,16 +2907,26 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ số sản xuất công nghiệp IIP ngành sản xuất kim loại cấp 2 (mã 24) theo GSO</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
           <t>gso_iip_metal_yoy</t>
         </is>
       </c>
-      <c r="J7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>ind_src_gso_industry_q3_2026</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -2473,20 +2937,20 @@
           <t>ind_pe_median</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>P/E trung vị ngành Công nghệ</t>
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>P/E trung vị nhóm so sánh (Peers Median P/E)</t>
         </is>
       </c>
       <c r="D8" s="6" t="n">
-        <v>20.65</v>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
+        <v>16.8</v>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F8" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
@@ -2501,18 +2965,26 @@
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="I8" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 3 peers: ITD (14.2), ELC (16.8), CMG (24.5) = 16.8x</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
         <is>
           <t>median_peer_pe</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
         <is>
           <t>ind_src_vietstock_tech_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -2523,46 +2995,54 @@
           <t>ind_pb_median</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>P/B trung vị ngành Công nghệ</t>
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>P/B trung vị nhóm so sánh (Peers Median P/B)</t>
         </is>
       </c>
       <c r="D9" s="6" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 3 peers: ITD (1.25), ELC (2.15), CMG (3.85) = 2.15x</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>median_peer_pb</t>
         </is>
       </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>ind_src_vietstock_tech_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -2573,20 +3053,20 @@
           <t>ind_roe_avg</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>ROE bình quân ngành Công nghệ</t>
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>ROE bình quân nhóm so sánh (Peers Mean ROE)</t>
         </is>
       </c>
       <c r="D10" s="6" t="n">
         <v>0.133</v>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F10" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
@@ -2601,18 +3081,26 @@
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="I10" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 3 peers: (0.165 + 0.142 + 0.092) / 3 = 0.133</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
         <is>
           <t>mean_peer_roe</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>ind_src_vietstock_tech_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -2620,795 +3108,1339 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
+          <t>ind_net_margin_avg</t>
+        </is>
+      </c>
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng bình quân nhóm so sánh</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 3 peers: (0.082 + 0.095 + 0.042) / 3 = 0.073</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t>mean_peer_net_margin</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_tech_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>FPT</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>ind_ict_export_growth</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Tăng trưởng kim ngạch xuất khẩu phần mềm &amp; dịch vụ CNTT 8T/2026</t>
-        </is>
-      </c>
-      <c r="D11" s="6" t="n">
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Tăng trưởng kim ngạch xuất khẩu dịch vụ CNTT 8T/2026 (YoY)</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="n">
         <v>0.178</v>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="3" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="3" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>Theo số liệu công bố lũy kế 8 tháng 2026 của Bộ Thông tin và Truyền thông</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
         <is>
           <t>mic_ict_export_yoy</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>ind_src_mic_stats_2026</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>ind_pe_median</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>P/E trung vị ngành Ngân hàng</t>
-        </is>
-      </c>
-      <c r="D12" s="6" t="n">
+      <c r="C13" s="3" t="inlineStr">
+        <is>
+          <t>P/E trung vị nhóm so sánh (Peers Median P/E)</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E13" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F13" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 5 peers: MBB (6.2), ACB (6.8), TCB (7.5), CTG (9.2), BID (11.8) = 7.5x</t>
+        </is>
+      </c>
+      <c r="K13" s="3" t="inlineStr">
+        <is>
+          <t>median_peer_pe</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_banking_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>ind_universe_median_pe</t>
+        </is>
+      </c>
+      <c r="C14" s="3" t="inlineStr">
+        <is>
+          <t>P/E trung vị toàn ngành (Toàn bộ 27 ngân hàng niêm yết)</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="n">
         <v>8.35</v>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="I14" s="6" t="n">
+        <v>27</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị định giá P/E toàn bộ 27 ngân hàng thương mại niêm yết theo dữ liệu Vietstock</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t>industry_universe_median_pe</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_banking_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>ind_pb_median</t>
+        </is>
+      </c>
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>P/B trung vị nhóm so sánh (Peers Median P/B)</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="E15" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F15" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 5 peers: MBB (1.12), TCB (1.15), ACB (1.35), CTG (1.42), BID (1.95) = 1.35x</t>
+        </is>
+      </c>
+      <c r="K15" s="3" t="inlineStr">
+        <is>
+          <t>median_peer_pb</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_banking_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>ind_roe_avg</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>ROE bình quân nhóm so sánh (Peers Mean ROE)</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>0.1908</v>
+      </c>
+      <c r="E16" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F16" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 5 peers: (0.178 + 0.165 + 0.168 + 0.215 + 0.228) / 5 = 0.1908</t>
+        </is>
+      </c>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t>mean_peer_roe</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_banking_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>ind_net_margin_avg</t>
+        </is>
+      </c>
+      <c r="C17" s="3" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng bình quân nhóm so sánh</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="E17" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F17" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 5 peers: (0.312 + 0.335 + 0.425 + 0.412 + 0.435) / 5 = 0.3838</t>
+        </is>
+      </c>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t>mean_peer_net_margin</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_banking_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>ind_credit_growth_system</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Tăng trưởng tín dụng toàn hệ thống 9 tháng 2026 (YTD)</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>0.092</v>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>Tăng trưởng tín dụng lũy kế so với đầu năm 2026 theo thông cáo của Ngân hàng Nhà nước</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t>sbv_credit_growth_ytd</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_sbv_credit_growth_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>VCB</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>ind_npl_ratio_system</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>Tỷ lệ nợ xấu nội bảng (NPL) trung bình ngành tại thời điểm Q2/2026</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>0.0245</v>
+      </c>
+      <c r="E19" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F19" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>Tỷ lệ nợ xấu nội bảng trung bình toàn hệ thống tại ngày 30/06/2026 theo báo cáo VNBA</t>
+        </is>
+      </c>
+      <c r="K19" s="3" t="inlineStr">
+        <is>
+          <t>vnba_npl_mean</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vnba_banking_report_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>MWG</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>ind_pe_median</t>
+        </is>
+      </c>
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>P/E trung vị nhóm so sánh (Peers Median P/E)</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>16.2</v>
+      </c>
+      <c r="E20" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F20" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 3 peers: PNJ (15.8), DGW (16.2), FRT (32.5) = 16.2x</t>
+        </is>
+      </c>
+      <c r="K20" s="3" t="inlineStr">
         <is>
           <t>median_peer_pe</t>
         </is>
       </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_banking_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>VCB</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_retail_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>MWG</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>ind_pb_median</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>P/B trung vị ngành Ngân hàng</t>
-        </is>
-      </c>
-      <c r="D13" s="6" t="n">
+      <c r="C21" s="3" t="inlineStr">
+        <is>
+          <t>P/B trung vị nhóm so sánh (Peers Median P/B)</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="E21" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F21" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 3 peers: DGW (2.85), PNJ (3.12), FRT (7.20) = 3.12x</t>
+        </is>
+      </c>
+      <c r="K21" s="3" t="inlineStr">
+        <is>
+          <t>median_peer_pb</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_retail_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>MWG</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>ind_roe_avg</t>
+        </is>
+      </c>
+      <c r="C22" s="3" t="inlineStr">
+        <is>
+          <t>ROE bình quân nhóm so sánh (Peers Mean ROE)</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>0.211667</v>
+      </c>
+      <c r="E22" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F22" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 3 peers: (0.225 + 0.175 + 0.235) / 3 = 0.211667</t>
+        </is>
+      </c>
+      <c r="K22" s="3" t="inlineStr">
+        <is>
+          <t>mean_peer_roe</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_retail_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>MWG</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>ind_net_margin_avg</t>
+        </is>
+      </c>
+      <c r="C23" s="3" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng bình quân nhóm so sánh</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0.032333</v>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 3 peers: (0.018 + 0.024 + 0.055) / 3 = 0.032333</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t>mean_peer_net_margin</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_retail_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>MWG</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>ind_retail_sales_growth</t>
+        </is>
+      </c>
+      <c r="C24" s="3" t="inlineStr">
+        <is>
+          <t>Tăng trưởng tổng mức bán lẻ tiêu dùng 9T/2026 (YoY danh nghĩa)</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="n">
+        <v>0.08799999999999999</v>
+      </c>
+      <c r="E24" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F24" s="3" t="inlineStr">
+        <is>
+          <t>quarterly</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2026-01-01</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>Tăng trưởng tổng mức bán lẻ hàng hóa và doanh thu dịch vụ 9 tháng 2026 danh nghĩa theo GSO</t>
+        </is>
+      </c>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t>gso_retail_growth_yoy</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_gso_retail_sales_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>ind_pe_median</t>
+        </is>
+      </c>
+      <c r="C25" s="3" t="inlineStr">
+        <is>
+          <t>P/E trung vị nhóm so sánh (Peers Median P/E)</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>24.5</v>
+      </c>
+      <c r="E25" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 3 peers: NLG (22.8), KDH (24.5), DXG (35.2) = 24.5x</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>median_peer_pe</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_bds_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>ind_pb_median</t>
+        </is>
+      </c>
+      <c r="C26" s="3" t="inlineStr">
+        <is>
+          <t>P/B trung vị nhóm so sánh (Peers Median P/B)</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="n">
         <v>1.35</v>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E26" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F26" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I26" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 3 peers: DXG (1.15), NLG (1.35), KDH (1.75) = 1.35x</t>
+        </is>
+      </c>
+      <c r="K26" s="3" t="inlineStr">
         <is>
           <t>median_peer_pb</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_banking_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>VCB</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_bds_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>ind_roe_avg</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>ROE bình quân ngành Ngân hàng</t>
-        </is>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>0.1908</v>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="C27" s="3" t="inlineStr">
+        <is>
+          <t>ROE bình quân nhóm so sánh (Peers Mean ROE)</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>0.059333</v>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F27" s="3" t="inlineStr">
         <is>
           <t>annual</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr">
         <is>
           <t>2025-01-01</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>2025-12-31</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="I27" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 3 peers: (0.075 + 0.068 + 0.035) / 3 = 0.059333</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
         <is>
           <t>mean_peer_roe</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_banking_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>VCB</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>ind_credit_growth_system</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Tăng trưởng tín dụng toàn hệ thống 9 tháng 2026</t>
-        </is>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_bds_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>ind_net_margin_avg</t>
+        </is>
+      </c>
+      <c r="C28" s="3" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng bình quân nhóm so sánh</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="E28" s="3" t="inlineStr">
         <is>
           <t>ratio</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
+      <c r="F28" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I28" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 3 peers: (0.285 + 0.165 + 0.045) / 3 = 0.165</t>
+        </is>
+      </c>
+      <c r="K28" s="3" t="inlineStr">
+        <is>
+          <t>mean_peer_net_margin</t>
+        </is>
+      </c>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_bds_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>ind_pe_median</t>
+        </is>
+      </c>
+      <c r="C29" s="3" t="inlineStr">
+        <is>
+          <t>P/E trung vị nhóm so sánh (Peers Median P/E)</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="E29" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F29" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 3 peers: VND (13.8), HCM (15.2), VCI (16.5) = 15.2x</t>
+        </is>
+      </c>
+      <c r="K29" s="3" t="inlineStr">
+        <is>
+          <t>median_peer_pe</t>
+        </is>
+      </c>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_sec_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>ind_pb_median</t>
+        </is>
+      </c>
+      <c r="C30" s="3" t="inlineStr">
+        <is>
+          <t>P/B trung vị nhóm so sánh (Peers Median P/B)</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="E30" s="3" t="inlineStr">
+        <is>
+          <t>x</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>Trung vị của 3 peers: VND (1.35), HCM (1.85), VCI (2.15) = 1.85x</t>
+        </is>
+      </c>
+      <c r="K30" s="3" t="inlineStr">
+        <is>
+          <t>median_peer_pb</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_sec_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>ind_roe_avg</t>
+        </is>
+      </c>
+      <c r="C31" s="3" t="inlineStr">
+        <is>
+          <t>ROE bình quân nhóm so sánh (Peers Mean ROE)</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>0.141667</v>
+      </c>
+      <c r="E31" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F31" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 3 peers: (0.155 + 0.125 + 0.145) / 3 = 0.141667</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t>mean_peer_roe</t>
+        </is>
+      </c>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_sec_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>ind_net_margin_avg</t>
+        </is>
+      </c>
+      <c r="C32" s="3" t="inlineStr">
+        <is>
+          <t>Biên lợi nhuận ròng bình quân nhóm so sánh</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>0.358333</v>
+      </c>
+      <c r="E32" s="3" t="inlineStr">
+        <is>
+          <t>ratio</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>2025-01-01</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>Trung bình cộng 3 peers: (0.385 + 0.325 + 0.365) / 3 = 0.358333</t>
+        </is>
+      </c>
+      <c r="K32" s="3" t="inlineStr">
+        <is>
+          <t>mean_peer_net_margin</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_sec_benchmark</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>ind_adtv_market</t>
+        </is>
+      </c>
+      <c r="C33" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị giao dịch bình quân phiên (ADTV) toàn thị trường 9 tháng 2026</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>22000000000000</v>
+      </c>
+      <c r="E33" s="3" t="inlineStr">
+        <is>
+          <t>VND</t>
+        </is>
+      </c>
+      <c r="F33" s="3" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
         <is>
           <t>2026-01-01</t>
         </is>
       </c>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>sbv_credit_growth_ytd</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_sbv_credit_growth_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>VCB</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>ind_npl_ratio_system</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Tỷ lệ nợ xấu nội bảng (NPL) trung bình ngành</t>
-        </is>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>0.0245</v>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>vnba_npl_mean</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vnba_banking_report_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>MWG</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>ind_pe_median</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>P/E trung vị ngành Bán lẻ</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>median_peer_pe</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_retail_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>MWG</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>ind_pb_median</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>P/B trung vị ngành Bán lẻ</t>
-        </is>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>median_peer_pb</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_retail_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>MWG</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>ind_roe_avg</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>ROE bình quân ngành Bán lẻ</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>0.2117</v>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>mean_peer_roe</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_retail_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>MWG</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>ind_retail_sales_growth</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Tăng trưởng tổng mức bán lẻ tiêu dùng 9T/2026</t>
-        </is>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>0.08799999999999999</v>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>quarterly</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2026-01-01</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>gso_retail_growth_yoy</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_gso_retail_sales_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>VHM</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>ind_pe_median</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>P/E trung vị ngành Bất động sản</t>
-        </is>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>24.5</v>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>median_peer_pe</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_bds_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>VHM</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>ind_pb_median</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>P/B trung vị ngành Bất động sản</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>median_peer_pb</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_bds_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>VHM</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>ind_roe_avg</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>ROE bình quân ngành Bất động sản</t>
-        </is>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>0.0593</v>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>mean_peer_roe</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_bds_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>SSI</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>ind_pe_median</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>P/E trung vị ngành Chứng khoán</t>
-        </is>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>15.2</v>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>median_peer_pe</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_sec_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>SSI</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>ind_pb_median</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>P/B trung vị ngành Chứng khoán</t>
-        </is>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>x</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>median_peer_pb</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_sec_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>SSI</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>ind_roe_avg</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>ROE bình quân ngành Chứng khoán</t>
-        </is>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>0.1417</v>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>ratio</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>annual</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2025-01-01</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2025-12-31</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>mean_peer_roe</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_sec_benchmark</t>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>Giá trị giao dịch khớp lệnh bình quân phiên 3 sàn (HOSE, HNX, UPCOM) 9 tháng đầu năm 2026</t>
+        </is>
+      </c>
+      <c r="K33" s="3" t="inlineStr">
+        <is>
+          <t>mean_daily_turnover</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>ind_src_ssc_krx_operation_2025</t>
         </is>
       </c>
     </row>
@@ -3423,13 +4455,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3445,16 +4479,26 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Nội Dung Nhận Định Ngành</t>
+          <t>Nội Dung Nhận Định Khách Quan</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Phân Loại Phát Biểu</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Thời Hạn Tác Động</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Truy Vết Bằng Chứng (Evidence Refs)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -3465,18 +4509,28 @@
           <t>ind_f01_steel_recovery</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Ngành thép đang bước vào pha phục hồi vững chắc của chu kỳ (Early Expansion). Động lực tiêu thụ đến từ 2 mũi nhọn: tiến độ giải ngân đầu tư công các dự án đại hạ tầng (Sân bay Long Thành, cao tốc Bắc - Nam) và thị trường bất động sản dân cư ấm dần trở lại theo đà tháo gỡ pháp lý của 3 bộ luật sửa đổi (Luật Đất đai, Nhà ở, Kinh doanh BĐS).</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Ngành thép đang trong pha phục hồi chu kỳ (Recovery Phase). Quan sát từ dữ liệu cho thấy tăng trưởng tiêu thụ thép xây dựng và HRC đạt 11.8% YoY trong 8T/2026 cùng chỉ số IIP sản xuất kim loại tăng 10.6% YoY. Cơ chế hỗ trợ chính đến từ tiến độ giải ngân đầu tư công các dự án đại hạ tầng giao thông và số lượng dự án nhà ở hoàn thành các bước pháp lý sơ bộ sau khi các luật sửa đổi có hiệu lực từ tháng 8/2024.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>Trung hạn 6 - 12 tháng</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>ind_src_vsa_report_2026, ind_crude_steel_consumption_growth, ind_iip_metal_growth</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -3487,18 +4541,28 @@
           <t>ind_f02_trade_defense</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Bộ Công Thương thụ lý điều tra chống bán phá giá sản phẩm HRC nhập khẩu từ Trung Quốc và Ấn Độ là 'lá chắn' chính sách mang tính bước ngoặt, tạo tiền đề nâng cao tỷ trọng tiêu thụ thép HRC tự chủ nội địa và bảo vệ biên lợi nhuận của các nhà sản xuất có chu trình khép kín như Hòa Phát.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_moit_trade_defense_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Chính sách phòng vệ thương mại có bước tiến then chốt khi Bộ Công Thương ban hành Quyết định 1959/QĐ-BCT ngày 04/07/2025 áp dụng biện pháp chống bán phá giá chính thức đối với một số sản phẩm thép cuộn cán nóng (HRC) nhập khẩu từ Trung Quốc. Quyết định này giúp hạn chế tình trạng bán phá giá và tạo điều kiện ổn định thị phần tiêu thụ nội địa cho các nhà sản xuất thép cán nóng trong nước.</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>MECHANISM</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>Trung hạn 12 - 24 tháng</t>
+        </is>
+      </c>
+      <c r="F3" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_moit_ad20_decision_1985, ind_src_moit_ad20_decision_1959</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -3509,18 +4573,28 @@
           <t>ind_f03_competitive_moat</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Phân hóa vị thế cạnh tranh cực kỳ sâu sắc trong ngành: Doanh nghiệp sở hữu công nghệ lò cao liên hợp BOF khép kín quy mô lớn (như Hòa Phát với cụm Dung Quất) đạt giá thành sản xuất phôi và HRC thấp hơn từ 15-20% so với lò điện EAF phế liệu của các đối thủ nhỏ lẻ, tạo rào cản chi phí vững chắc.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Khảo sát cấu trúc ngành cho thấy lợi thế quy mô rõ rệt: Các tổ hợp lò cao khép kín BOF (như dự án Dung Quất của Hòa Phát) có lợi thế cạnh tranh về giá thành sản xuất phôi thép và HRC so với công nghệ lò điện EAF phế liệu nhỏ lẻ, nhờ khả năng tối ưu hóa nhiệt luyện liên tục và đàm phán giá quặng sắt/than cốc khối lượng lớn.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>Dài hạn</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_steel_benchmark, ind_net_margin_avg</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -3531,18 +4605,28 @@
           <t>ind_f01_ai_digital_wave</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Ngành Công nghệ thông tin Việt Nam đang ở pha tăng trưởng mở rộng (Expansion Stage) mạnh mẽ nhất trong thập kỷ. Làn sóng ứng dụng Trí tuệ nhân tạo (GenAI), điện toán đám mây và nhu cầu chuyển đổi số toàn cầu từ các thị trường trọng điểm (Nhật Bản, Bắc Mỹ, Châu Âu, APAC) thúc đẩy hợp đồng ký mới tăng trưởng hai chữ số bền vững.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Ngành Công nghệ thông tin Việt Nam duy trì đà tăng trưởng tích cực (Expansion Stage). Dữ liệu ngành 8 tháng 2026 cho thấy kim ngạch xuất khẩu dịch vụ CNTT tăng trưởng 17.8% YoY, dẫn dắt bởi nhu cầu chuyển đổi số doanh nghiệp, triển khai giải pháp điện toán đám mây và ứng dụng trí tuệ nhân tạo (AI) từ các thị trường quốc tế trọng điểm như Nhật Bản, Bắc Mỹ và khu vực Châu Á - Thái Bình Dương.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t>Trung hạn 6 - 12 tháng</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>ind_src_vinasa_report_2026, ind_ict_export_growth</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -3553,18 +4637,28 @@
           <t>ind_f02_cost_advantage_vietnam</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Lợi thế chi phí nhân lực công nghệ thông tin và tháp dân số trẻ của Việt Nam tiếp tục là điểm tựa cạnh tranh xuất sắc so với Ấn Độ và Đông Âu. Doanh nghiệp đầu ngành như FPT có khả năng mở rộng quy mô hợp đồng lên cấp độ Mega-deal (&gt;100 triệu USD) nhờ năng lực cung ứng trọn gói từ tư vấn chiến lược đến triển khai giải pháp chuyên sâu.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_mic_stats_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Lợi thế nguồn nhân lực công nghệ số trẻ với chi phí cạnh tranh tiếp tục là bệ phóng giúp các doanh nghiệp phần mềm Việt Nam duy trì biên lợi nhuận hoạt động ổn định. Đối với các đơn vị đầu ngành có quy mô nhân sự lớn, việc tích lũy kinh nghiệm chuyên ngành (Domain Expertise) và đối tác công nghệ toàn cầu tạo điều kiện tiếp cận các gói thầu chuyển đổi số quy mô lớn.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>MECHANISM</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
+        <is>
+          <t>Dài hạn</t>
+        </is>
+      </c>
+      <c r="F6" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_mic_stats_2026, ind_net_margin_avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
@@ -3575,18 +4669,28 @@
           <t>ind_f01_credit_acceleration</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Ngành Ngân hàng đang trong pha tăng tốc chu kỳ tín dụng (Credit Acceleration Phase). Ngân hàng Nhà nước chủ động giao toàn bộ hạn mức room tín dụng 15% ngay từ đầu năm cùng định hướng duy trì mặt bằng lãi suất cho vay thấp để thúc đẩy sản xuất kinh doanh, giúp tăng trưởng tín dụng phục hồi vững chắc.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Ngành Ngân hàng đang trong pha phục hồi chu kỳ tín dụng (Credit Recovery Phase). Ngân hàng Nhà nước duy trì định hướng chỉ tiêu tăng trưởng tín dụng toàn hệ thống khoảng 15% cho cả năm 2026 và giao hạn mức linh hoạt, hỗ trợ tốc độ tăng trưởng tín dụng 9 tháng đạt 9.2% YTD trong bối cảnh thanh khoản hệ thống dồi dào và lãi suất cho vay ở mức hợp lý.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
+        <is>
+          <t>Trung hạn 6 - 12 tháng</t>
+        </is>
+      </c>
+      <c r="F7" s="3" t="inlineStr">
         <is>
           <t>ind_src_sbv_credit_growth_2026, ind_credit_growth_system</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
@@ -3597,18 +4701,28 @@
           <t>ind_f02_asset_quality_differentiation</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Sự phân hóa rõ nét về chất lượng tài sản và chi phí dự phòng: Các ngân hàng có tỷ lệ bao phủ nợ xấu (LLR) cao vượt trội (như Vietcombank đạt trên 200%) có bộ đệm trích lập an toàn tuyệt đối, giúp chủ động hoàn nhập dự phòng và duy trì đà tăng trưởng lợi nhuận trước thuế bền vững so với các ngân hàng nhỏ lẻ.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vnba_banking_report_2026, ind_npl_ratio_system</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Chất lượng tài sản và bộ đệm trích lập dự phòng có sự phân hóa đáng kể: Nhóm ngân hàng có tỷ lệ bao phủ nợ xấu (LLR) cao và tỷ lệ CASA vượt trội có lợi thế rõ rệt về chi phí vốn (COF) và khả năng kiểm soát chi phí tín dụng (Credit Cost), qua đó tạo điều kiện duy trì biên lãi thuần NIM ổn định hơn so với nhóm ngân hàng quy mô nhỏ.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>MECHANISM</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
+        <is>
+          <t>Trung hạn 12 tháng</t>
+        </is>
+      </c>
+      <c r="F8" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_vnba_banking_report_2026, ind_npl_ratio_system, ind_net_margin_avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
@@ -3619,18 +4733,28 @@
           <t>ind_f01_retail_consumption_rebound</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Sức mua của người tiêu dùng nội địa đang phục hồi rõ nét sau các biện pháp giảm thuế VAT 2% và tăng lương cơ sở, giúp doanh thu bán lẻ toàn ngành cải thiện tốc độ tăng trưởng.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Sức cầu tiêu dùng bán lẻ ghi nhận đà cải thiện dần với mức tăng trưởng tổng mức bán lẻ hàng hóa và dịch vụ 9T/2026 đạt 8.8% YoY. Các chính sách hỗ trợ tài khóa như giảm thuế VAT 2% và điều chỉnh tăng lương cơ sở góp phần ổn định sức mua, tuy nhiên mức độ phục hồi có sự phân hóa theo từng nhóm mặt hàng thiết yếu và không thiết yếu.</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>OBSERVATION</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
+        <is>
+          <t>Ngắn - Trung hạn</t>
+        </is>
+      </c>
+      <c r="F9" s="3" t="inlineStr">
         <is>
           <t>ind_src_gso_retail_sales_2026, ind_retail_sales_growth</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
@@ -3641,18 +4765,28 @@
           <t>ind_f02_retail_consolidation</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Xu hướng tinh gọn mạng lưới cửa hàng không hiệu quả, tối ưu hóa chuỗi cung ứng và mở rộng mô hình bán lẻ đa kênh (Omni-channel) giúp các chuỗi lớn mở rộng biên lợi nhuận hoạt động.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vietstock_retail_benchmark</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Xu hướng tái cơ cấu mạng lưới cửa hàng và tối ưu hóa chi phí vận hành: Các chuỗi bán lẻ quy mô lớn tập trung đóng các điểm bán kém hiệu quả, tối ưu hóa vòng quay hàng tồn kho và thúc đẩy doanh thu bán hàng đa kênh (Omni-channel), giúp bảo vệ biên lợi nhuận hoạt động trong giai đoạn sức mua đang hồi phục.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>MECHANISM</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
+        <is>
+          <t>Trung hạn 12 tháng</t>
+        </is>
+      </c>
+      <c r="F10" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_vietstock_retail_benchmark, ind_net_margin_avg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -3663,18 +4797,28 @@
           <t>ind_f01_legal_framework_unlock</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Hiệu lực thực thi của 3 bộ luật (Luật Đất đai, Luật Nhà ở, Luật Kinh doanh BĐS) tháo gỡ điểm nghẽn phê duyệt pháp lý dự án, giúp khơi thông nguồn cung mới từ cuối năm 2026.</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_vars_real_estate_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Khung khổ pháp lý thị trường bất động sản ghi nhận bước ngoặt khi 3 đạo luật lớn (Luật Đất đai, Luật Nhà ở, Luật Kinh doanh BĐS) chính thức có hiệu lực từ ngày 01/08/2024. Việc áp dụng các nghị định hướng dẫn đang từng bước tháo gỡ điểm nghẽn về tính tiền sử dụng đất và cấp phép dự án tại các đô thị lớn, tạo tiền đề cải thiện nguồn cung nhà ở thương mại trung và dài hạn.</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>MECHANISM</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
+        <is>
+          <t>Trung - Dài hạn 12 - 24 tháng</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_gov_real_estate_laws_effective, ind_src_vars_real_estate_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
           <t>SSI</t>
@@ -3685,14 +4829,24 @@
           <t>ind_f01_upgrade_ftse_krx</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Triển vọng nâng hạng thị trường chứng khoán Việt Nam từ cận biên (Frontier) lên mới nổi thứ cấp (Secondary Emerging Market) của FTSE Russell cùng vận hành hệ thống KRX là cú hích thanh khoản mang tính chu kỳ lớn cho toàn bộ các CTCK.</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_ssc_market_liquidity_2026</t>
+      <c r="C12" s="3" t="inlineStr">
+        <is>
+          <t>Hạ tầng kỹ thuật thị trường chứng khoán được nâng cấp toàn diện sau khi hệ thống KRX chính thức vận hành từ 05/05/2025. Cùng với đó, việc FTSE Russell công bố lộ trình có hiệu lực phân loại thị trường mới nổi thứ cấp (Secondary Emerging Market) từ ngày 21/09/2026 và triển khai theo các đợt tiếp theo mở ra cơ hội gia tăng dòng vốn ngoại và cải thiện thanh khoản giao dịch chung của toàn ngành.</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="inlineStr">
+        <is>
+          <t>MECHANISM</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t>Trung hạn 12 tháng</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_ssc_krx_operation_2025, ind_src_ftse_russell_reclassification_2026, ind_adtv_market</t>
         </is>
       </c>
     </row>
@@ -3707,13 +4861,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="38" customWidth="1" min="4" max="4"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -3729,16 +4884,21 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Nội Dung Rủi Ro Ngành</t>
+          <t>Nội Dung Rủi Ro Ngành &amp; Biến Theo Dõi</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>Phân Loại Rủi Ro</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Truy Vết Bằng Chứng (Evidence Refs)</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -3749,18 +4909,23 @@
           <t>ind_r01_raw_material_volatility</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>Biến động giá nguyên vật liệu đầu vào toàn cầu: Giá quặng sắt (Iron Ore 62% Fe) và than mỡ luyện cốc (Coking Coal) chiếm 65-70% giá thành phôi thép. Nếu giá hàng hóa thế giới biến động bất thường do biến động cung ứng tại Úc/Brazil sẽ gây áp lực trực tiếp lên biên lợi nhuận gộp.</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>Biến động giá nguyên vật liệu thượng nguồn toàn cầu: Giá quặng sắt và than mỡ luyện cốc thế giới chiếm tỷ trọng lớn trong cơ cấu chi phí sản xuất phôi. Biến động nguồn cung từ các mỏ khai thác tại Úc và Brazil có thể tạo áp lực trực tiếp lên biên lợi nhuận gộp của các doanh nghiệp luyện kim.</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>RAW_MATERIAL</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>ind_src_vsa_report_2026</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="20" customHeight="1">
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -3771,18 +4936,23 @@
           <t>ind_r02_dumping_pressure</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Áp lực dư thừa công suất từ thị trường thép Trung Quốc: Ngành bất động sản Trung Quốc tăng trưởng chậm làm gia tăng áp lực đẩy thép giá rẻ xuất khẩu sang khu vực Đông Nam Á, tạo sức ép cạnh tranh giá bán nội địa trong ngắn hạn nếu rào cản phòng vệ thương mại chưa kịp áp thuế tạm thời.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_moit_trade_defense_2026</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Rủi ro cạnh tranh thương mại và kiểm soát nguồn gốc xuất xứ: Áp lực dư thừa công suất sản xuất thép từ khu vực và nguy cơ gian lận xuất xứ hàng hóa xuất khẩu có thể dẫn tới các cuộc điều tra tự vệ mới từ các thị trường nhập khẩu lớn (Mỹ, EU).</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_moit_ad20_decision_1959</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
@@ -3793,18 +4963,23 @@
           <t>ind_r03_carbon_green_transition</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Yêu cầu chuyển đổi xanh và cơ chế CBAM của Liên minh Châu Âu: Tiêu chuẩn phát thải carbon khắt khe đối với thép nhập khẩu vào EU đặt ra thách thức về chi phí đầu tư công nghệ giảm phát thải (Green Steel) đối với các đơn hàng xuất khẩu chất lượng cao.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Thách thức tuân thủ lộ trình chuyển đổi phát thải carbon thấp và cơ chế CBAM: Các tiêu chuẩn báo cáo phát thải khí nhà kính đối với thép xuất khẩu đòi hỏi doanh nghiệp phải bố trí vốn đầu tư công nghệ giảm phát thải (Green Steel) trong trung và dài hạn.</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>REGULATORY</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_steel_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="20" customHeight="1">
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -3815,18 +4990,23 @@
           <t>ind_r01_macro_slowdown_abroad</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Rủi ro suy thoái kinh tế hoặc cắt giảm ngân sách IT tại các thị trường trọng điểm: Doanh nghiệp xuất khẩu phần mềm phụ thuộc lớn vào chi tiêu công nghệ tại Mỹ và Nhật Bản. Nếu lãi suất neo cao kéo dài làm các tập đoàn đa quốc gia thắt chặt ngân sách R&amp;D/IT sẽ ảnh hưởng đến tốc độ tăng trưởng ký mới hợp đồng.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Rủi ro biến động ngân sách chi tiêu công nghệ tại các thị trường xuất khẩu trọng điểm: Xuất khẩu phần mềm chịu ảnh hưởng gián tiếp nếu các tập đoàn đa quốc gia tại Mỹ hoặc Nhật Bản trì hoãn kế hoạch đầu tư hệ thống mới trong bối cảnh tăng trưởng kinh tế toàn cầu có sự phân hóa.</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>ind_src_vinasa_report_2026</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="20" customHeight="1">
+    <row r="6" ht="22" customHeight="1">
       <c r="A6" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
@@ -3837,18 +5017,23 @@
           <t>ind_r02_fx_volatility_jpy_usd</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Biến động tỷ giá hối đoái: Tỷ trọng doanh thu lớn từ đồng Yên Nhật (JPY) và USD tiềm ẩn rủi ro chênh lệch tỷ giá kế toán khi đồng JPY suy yếu hoặc biến động mạnh so với VND.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
+        <is>
+          <t>Rủi ro biến động tỷ giá hối đoái đối với doanh thu ngoại tệ: Các hợp đồng phần mềm thanh toán bằng đồng Yên Nhật (JPY) hoặc USD có thể chịu ảnh hưởng chênh lệch tỷ giá kế toán nếu các đồng tiền này biến động mạnh so với VND mà chưa có công cụ phòng ngừa rủi ro tương ứng.</t>
+        </is>
+      </c>
+      <c r="D6" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_tech_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="20" customHeight="1">
+    <row r="7" ht="22" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
@@ -3859,18 +5044,23 @@
           <t>ind_r01_npl_real_estate</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Rủi ro nợ xấu tiềm ẩn và tái cơ cấu nợ: Mặc dù Thông tư giãn hoãn nợ hỗ trợ doanh nghiệp vượt qua giai đoạn khó khăn, nhưng áp lực nợ xấu chuyển nhóm vẫn là yếu tố cần theo dõi chặt chẽ nếu thanh khoản thị trường trái phiếu doanh nghiệp và bất động sản phục hồi chậm hơn kỳ vọng.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
+        <is>
+          <t>Rủi ro nợ xấu tiềm ẩn và áp lực trích lập dự phòng bổ sung: Diễn biến thanh khoản của các doanh nghiệp bất động sản và tiến độ xử lý tài sản bảo đảm là yếu tố then chốt quyết định mức độ phát sinh nợ nhóm 2 và nợ xấu mới của ngành ngân hàng.</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>CREDIT</t>
+        </is>
+      </c>
+      <c r="E7" s="3" t="inlineStr">
         <is>
           <t>ind_src_vnba_banking_report_2026</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="20" customHeight="1">
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
@@ -3881,18 +5071,23 @@
           <t>ind_r02_nim_compression</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Áp lực thu hẹp biên lãi thuần (NIM): Cạnh tranh gay gắt về lãi suất cho vay đầu ra để giành thị phần khách hàng chất lượng cao trong khi lãi suất huy động đầu vào có dấu hiệu chạm đáy và nhích nhẹ.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
+        <is>
+          <t>Áp lực thu hẹp biên lãi thuần (NIM): Mức độ cạnh tranh lãi suất cho vay đối với nhóm khách hàng doanh nghiệp chất lượng cao, cùng khả năng lãi suất huy động tiền gửi điều chỉnh tăng nhẹ ở các kỳ hạn dài có thể gây áp lực lên biên lãi ròng của các ngân hàng có tỷ lệ CASA thấp.</t>
+        </is>
+      </c>
+      <c r="D8" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="E8" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_banking_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
+    <row r="9" ht="22" customHeight="1">
       <c r="A9" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
@@ -3903,18 +5098,23 @@
           <t>ind_r01_consumer_sentiment_risk</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Rủi ro tâm lý người tiêu dùng thắt chặt chi tiêu các sản phẩm công nghệ không thiết yếu (ICT/CE) nếu áp lực chi phí sinh hoạt gia tăng.</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
+        <is>
+          <t>Rủi ro phân hóa sức mua và chi tiêu thận trọng: Tốc độ tăng trưởng thu nhập thực tế của người tiêu dùng và áp lực chi phí sinh hoạt có thể ảnh hưởng đến quyết định nâng cấp sản phẩm công nghệ cao cấp (ICT/CE).</t>
+        </is>
+      </c>
+      <c r="D9" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="E9" s="3" t="inlineStr">
         <is>
           <t>ind_src_gso_retail_sales_2026</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="20" customHeight="1">
+    <row r="10" ht="22" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
           <t>VHM</t>
@@ -3925,18 +5125,23 @@
           <t>ind_r01_bond_maturity_pressure</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>Áp lực đáo hạn trái phiếu doanh nghiệp và dòng tiền thu tiền theo tiến độ xây dựng vẫn là bài toán sống còn đối với các chủ đầu tư đòn bẩy tài chính cao.</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
+        <is>
+          <t>Áp lực dòng tiền và nghĩa vụ đáo hạn trái phiếu doanh nghiệp: Mặc dù các vướng mắc pháp lý đang được tháo gỡ, áp lực tái cấp vốn và cân đối dòng tiền để thanh toán các lô trái phiếu đến hạn vẫn là rủi ro cần theo dõi chặt chẽ đối với các chủ đầu tư có tỷ lệ nợ vay cao.</t>
+        </is>
+      </c>
+      <c r="D10" s="3" t="inlineStr">
+        <is>
+          <t>LIQUIDITY</t>
+        </is>
+      </c>
+      <c r="E10" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_bds_benchmark</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="20" customHeight="1">
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
           <t>SSI</t>
@@ -3947,12 +5152,17 @@
           <t>ind_r01_market_volatility_fvtpl</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Biến động mạnh của chỉ số VN-Index ảnh hưởng trực tiếp đến kết quả đánh giá lại danh mục tài sản tài chính tự doanh (FVTPL) và thanh khoản dư nợ cho vay ký quỹ (Margin).</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
+        <is>
+          <t>Rủi ro biến động chỉ số thị trường và danh mục tự doanh FVTPL: Kết quả kinh doanh của các công ty chứng khoán có độ nhạy cao với biến động điểm số VN-Index và mức độ biến động định giá các cổ phiếu trong danh mục tài sản tài chính ghi nhận qua lãi/lỗ (FVTPL).</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="inlineStr">
+        <is>
+          <t>MARKET</t>
+        </is>
+      </c>
+      <c r="E11" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_sec_benchmark</t>
         </is>
@@ -3969,17 +5179,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:I20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
-    <col width="48" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="52" customWidth="1" min="3" max="3"/>
+    <col width="52" customWidth="1" min="4" max="4"/>
+    <col width="26" customWidth="1" min="5" max="5"/>
     <col width="28" customWidth="1" min="6" max="6"/>
-    <col width="48" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="52" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
@@ -4005,7 +5216,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Ngày Công Bố</t>
+          <t>Ngày Ban Hành / Công Bố</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -4020,27 +5231,32 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Đã Kiểm Ngày</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
+          <t>Người Kiểm Chứng</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Trạng Thái Xác Minh</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>ind_src_vsa_report_2026</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Hiệp hội Thép Việt Nam (VSA) - Báo cáo tổng kết tình hình sản xuất và bán hàng thép xây dựng, HRC 8 tháng đầu năm 2026</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>http://vsa.com.vn/tinh-hinh-san-xuat-va-tieu-thu-thep-viet-nam/</t>
         </is>
@@ -4055,34 +5271,39 @@
           <t>2026-10-09T08:00:00+07:00</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Mục 2.1 &amp; 2.3: Sản lượng bán hàng HRC và thép xây dựng toàn ngành</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>Mục 2.1 &amp; 2.3: Sản lượng bán hàng HRC và thép xây dựng toàn ngành 8T/2026</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Đối chiếu số liệu báo cáo bản tin tháng 8/2026 của VSA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
         <is>
           <t>ind_src_gso_industry_q3_2026</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Tổng cục Thống kê (GSO) - Báo cáo Tình hình kinh tế - xã hội 9 tháng năm 2026 (Chỉ số sản xuất công nghiệp IIP ngành kim loại)</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>Tổng cục Thống kê (GSO) - Báo cáo Tình hình kinh tế - xã hội 9 tháng năm 2026 (Chỉ số sản xuất công nghiệp IIP ngành sản xuất kim loại)</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
         <is>
           <t>https://www.gso.gov.vn/du-lieu-va-so-lieu-thong-ke/2026/09/tinh-hinh-kinh-te-xa-hoi-9-thang-nam-2026/</t>
         </is>
@@ -4097,41 +5318,46 @@
           <t>2026-10-09T08:15:00+07:00</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Biểu số 4: Chỉ số sản xuất ngành sản xuất kim loại đúc sẵn</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
+      <c r="G3" s="3" t="inlineStr">
+        <is>
+          <t>Biểu số 4: Chỉ số sản xuất ngành sản xuất kim loại (Ngành cấp 2 mã 24)</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Đối chiếu Niên giám số liệu kinh tế - xã hội Quý 3/2026 GSO</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="22" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_moit_trade_defense_2026</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Cục Phòng vệ thương mại - Bộ Công Thương: Thông báo quyết định điều tra chống bán phá giá đối với một số sản phẩm thép cuộn cán nóng (HRC) từ Trung Quốc và Ấn Độ</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_moit_ad20_decision_1985</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Bộ Công Thương - Quyết định số 1985/QĐ-BCT ngày 26/07/2024 về việc điều tra áp dụng biện pháp chống bán phá giá đối với thép cán nóng (HRC) từ Trung Quốc và Ấn Độ</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>http://trav.gov.vn/thong-bao-dieu-tra-chong-ban-pha-gia-hrc.html</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2024-07-26</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -4139,560 +5365,771 @@
           <t>2026-10-09T08:30:00+07:00</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Quyết định số 1985/QĐ-BCT</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định 1985/QĐ-BCT, Cục Phòng vệ thương mại</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Đã đính chính năm ban hành văn bản chính thức là 2024 (S1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
           <t>HPG</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_moit_ad20_decision_1959</t>
+        </is>
+      </c>
+      <c r="C5" s="3" t="inlineStr">
+        <is>
+          <t>Bộ Công Thương - Quyết định số 1959/QĐ-BCT ngày 04/07/2025 áp dụng thuế chống bán phá giá chính thức đối với một số sản phẩm thép cuộn cán nóng (HRC) xuất xứ Trung Quốc và chấm dứt điều tra đối với Ấn Độ</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
+          <t>http://trav.gov.vn/quyet-dinh-ap-thue-chong-ban-pha-gia-hrc-1959.html</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T08:35:00+07:00</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>Quyết định 1959/QĐ-BCT ngày 04/07/2025 và Thông báo ngày 08/07/2025</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Bổ sung văn bản kết luận chính thức vụ việc AD20 (S2, S2a)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>HPG</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_steel_benchmark</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
+      <c r="C6" s="3" t="inlineStr">
         <is>
           <t>Vietstock Finance - Báo cáo Tổng quan định giá và chỉ số tài chính ngành Vật liệu xây dựng &amp; Thép năm 2025-2026</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D6" s="3" t="inlineStr">
         <is>
           <t>https://finance.vietstock.vn/nganh-nghe/1750/san-xuat-thep.htm</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:45:00+07:00</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Bảng thống kê P/E, P/B và ROE bình quân ngành Thép</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
+        <is>
+          <t>Bảng thống kê định giá P/E, P/B và ROE các doanh nghiệp ngành Thép</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Dữ liệu giá chốt phiên 30/09/2026 và BCTC kiểm toán năm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>ind_src_vinasa_report_2026</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
+      <c r="C7" s="3" t="inlineStr">
         <is>
           <t>Hiệp hội Phần mềm và Dịch vụ CNTT Việt Nam (VINASA) - Báo cáo Tổng quan Thị trường Công nghiệp ICT &amp; Xuất khẩu phần mềm Việt Nam 2025-2026</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D7" s="3" t="inlineStr">
         <is>
           <t>https://vinasa.org.vn/bao-cao-nganh-ict-viet-nam/</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:00:00+07:00</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Phần IV: Doanh thu dịch vụ phần mềm và chuyển đổi số toàn cầu của DN Việt Nam</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
+        <is>
+          <t>Phần IV: Doanh thu dịch vụ phần mềm và xuất khẩu giải pháp số của doanh nghiệp Việt Nam</t>
+        </is>
+      </c>
+      <c r="H7" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Đối chiếu bản báo cáo tổng kết thường niên VINASA tháng 8/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>ind_src_mic_stats_2026</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
+      <c r="C8" s="3" t="inlineStr">
         <is>
           <t>Bộ Thông tin và Truyền thông (MIC) - Niên giám thống kê công nghiệp công nghệ số và viễn thông 8 tháng 2026</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D8" s="3" t="inlineStr">
         <is>
           <t>https://mic.gov.vn/so-lieu-thong-ke-nganh-thong-tin-va-truyen-thong/</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:15:00+07:00</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Bảng 1.2: Doanh thu xuất khẩu dịch vụ CNTT và giải pháp số</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
+        <is>
+          <t>Bảng 1.2: Doanh thu xuất khẩu dịch vụ CNTT và giải pháp số 8T/2026</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Số liệu công bố chính thức trên cổng thông tin MIC</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>FPT</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_tech_benchmark</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
+      <c r="C9" s="3" t="inlineStr">
         <is>
           <t>Vietstock Finance - Báo cáo Định giá &amp; Hiệu quả vốn ngành Công nghệ thông tin Việt Nam 2026</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D9" s="3" t="inlineStr">
         <is>
           <t>https://finance.vietstock.vn/nganh-nghe/9530/phan-mem-dich-vu-may-tinh.htm</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:30:00+07:00</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Bảng P/E, P/B và ROE bình quân ngành Công nghệ</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
+        <is>
+          <t>Bảng thống kê P/E, P/B và ROE nhóm cổ phiếu CNTT niêm yết chốt phiên 30/09/2026</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Dữ liệu giá chốt phiên 30/09/2026 và BCTC kiểm toán năm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>ind_src_sbv_credit_growth_2026</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
+      <c r="C10" s="3" t="inlineStr">
         <is>
           <t>Ngân hàng Nhà nước Việt Nam (SBV) - Thông cáo điều hành chính sách tiền tệ và tăng trưởng tín dụng toàn hệ thống 9 tháng đầu năm 2026</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D10" s="3" t="inlineStr">
         <is>
           <t>https://sbv.gov.vn/webcenter/portal/vi/menu/trangchu/hoatdongnhnn/</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:00:00+07:00</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Mục 1: Tăng trưởng tín dụng toàn ngành đạt 9.2% so với đầu năm</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
+        <is>
+          <t>Mục 1: Tăng trưởng tín dụng toàn ngành đạt 9.2% YTD so với đầu năm 2026</t>
+        </is>
+      </c>
+      <c r="H10" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Thông cáo báo chí kỳ điều hành chính sách tiền tệ Quý 3/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>ind_src_vnba_banking_report_2026</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C11" s="3" t="inlineStr">
         <is>
           <t>Hiệp hội Ngân hàng Việt Nam (VNBA) - Báo cáo Tổng quan chất lượng tài sản, NIM và tỷ lệ bao phủ nợ xấu ngành Ngân hàng 2026</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D11" s="3" t="inlineStr">
         <is>
           <t>https://vnba.org.vn/bao-cao-tong-quan-hoat-dong-ngan-hang-viet-nam/</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:15:00+07:00</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Phần III: Phân tích biên lãi thuần NIM và tỷ lệ nợ xấu nội bảng NPL</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t>Phần III: Phân tích biên lãi thuần NIM và tỷ lệ nợ xấu nội bảng NPL các NHTM</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo thường niên VNBA tháng 8/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>VCB</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_banking_benchmark</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
+      <c r="C12" s="3" t="inlineStr">
         <is>
           <t>Vietstock Finance - Báo cáo Định giá P/B, P/E và ROE bình quân ngành Ngân hàng thương mại</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="D12" s="3" t="inlineStr">
         <is>
           <t>https://finance.vietstock.vn/nganh-nghe/8350/ngan-hang.htm</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:30:00+07:00</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Bảng P/B, P/E, ROE và ROA 27 ngân hàng niêm yết</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t>Bảng P/B, P/E, ROE và ROA nhóm ngân hàng thương mại niêm yết chốt phiên 30/09/2026</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Dữ liệu giá chốt phiên 30/09/2026 và BCTC kiểm toán năm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="3" t="inlineStr">
         <is>
           <t>ind_src_gso_retail_sales_2026</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
+      <c r="C13" s="3" t="inlineStr">
         <is>
           <t>Tổng cục Thống kê (GSO) - Báo cáo Tổng mức bán lẻ hàng hóa và doanh thu dịch vụ tiêu dùng 9 tháng năm 2026</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="D13" s="3" t="inlineStr">
         <is>
           <t>https://www.gso.gov.vn/du-lieu-va-so-lieu-thong-ke/2026/09/tong-muc-ban-le-hang-hoa-9-thang-nam-2026/</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:00:00+07:00</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>Chỉ tiêu tổng mức bán lẻ tăng 8.8% YoY</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t>Chỉ tiêu tổng mức bán lẻ hàng hóa và doanh thu dịch vụ tăng 8.8% YoY 9T/2026</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Số liệu công bố chính thức GSO Quý 3/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>MWG</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_retail_benchmark</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
+      <c r="C14" s="3" t="inlineStr">
         <is>
           <t>Vietstock Finance - Báo cáo Định giá &amp; Chỉ số tài chính ngành Bán lẻ 2026</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="D14" s="3" t="inlineStr">
         <is>
           <t>https://finance.vietstock.vn/nganh-nghe/5370/ban-le.htm</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:15:00+07:00</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>Bảng P/E, P/B và ROE ngành Bán lẻ</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
+        <is>
+          <t>Bảng P/E, P/B và ROE nhóm doanh nghiệp bán lẻ niêm yết chốt phiên 30/09/2026</t>
+        </is>
+      </c>
+      <c r="H14" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Dữ liệu giá chốt phiên 30/09/2026 và BCTC kiểm toán năm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>VHM</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>ind_src_vars_real_estate_2026</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Hội Môi giới Bất động sản Việt Nam (VARS) - Báo cáo Thị trường Bất động sản Việt Nam Quý 3/2026</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="3" t="inlineStr">
+        <is>
+          <t>Hội Môi giới Bất động sản Việt Nam (VARS) - Báo cáo Thị trường Bất động sản Việt Nam Quý 3/2026 (Bản ước tính sơ bộ)</t>
+        </is>
+      </c>
+      <c r="D15" s="3" t="inlineStr">
         <is>
           <t>https://vars.com.vn/bao-cao-thi-truong-bat-dong-san-viet-nam/</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:00:00+07:00</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>Mục 3: Tỷ lệ hấp thụ nguồn cung căn hộ và đất nền khu vực phía Nam &amp; phía Bắc</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="G15" s="3" t="inlineStr">
+        <is>
+          <t>Mục 3: Thống kê tỷ lệ hấp thụ nguồn cung nhà ở và giao dịch sơ bộ Q3/2026</t>
+        </is>
+      </c>
+      <c r="H15" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Báo cáo sơ bộ được công bố trước ngày kết thúc quý (S3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>VHM</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_gov_real_estate_laws_effective</t>
+        </is>
+      </c>
+      <c r="C16" s="3" t="inlineStr">
+        <is>
+          <t>Cổng Thông tin điện tử Chính phủ - Thông cáo hiệu lực thi hành 3 luật sửa đổi (Luật Đất đai, Luật Nhà ở, Luật Kinh doanh Bất động sản) từ ngày 01/08/2024</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="inlineStr">
+        <is>
+          <t>https://xaydungchinhsach.chinhphu.vn/hieu-luc-thi-hanh-3-luat-dat-dai-nha-o-kinh-doanh-bat-dong-san/</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2024-07-04</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T08:10:00+07:00</t>
+        </is>
+      </c>
+      <c r="G16" s="3" t="inlineStr">
+        <is>
+          <t>Văn bản Quốc hội thông qua cho phép 3 luật có hiệu lực sớm từ 01/08/2024</t>
+        </is>
+      </c>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Đối chiếu mốc hiệu lực chính thức của 3 luật từ 01/08/2024 (S3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>VHM</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_bds_benchmark</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
+      <c r="C17" s="3" t="inlineStr">
         <is>
           <t>Vietstock Finance - Báo cáo Định giá &amp; Cơ cấu nợ vay ngành Bất động sản dân cư 2026</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="D17" s="3" t="inlineStr">
         <is>
           <t>https://finance.vietstock.vn/nganh-nghe/8630/bat-dong-san.htm</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:15:00+07:00</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>Bảng P/B, P/E và D/E ngành Bất động sản</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="G17" s="3" t="inlineStr">
+        <is>
+          <t>Bảng P/B, P/E và D/E các doanh nghiệp phát triển BĐS niêm yết chốt phiên 30/09/2026</t>
+        </is>
+      </c>
+      <c r="H17" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Dữ liệu giá chốt phiên 30/09/2026 và BCTC kiểm toán năm 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>ind_src_ssc_market_liquidity_2026</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Ủy ban Chứng khoán Nhà nước (UBCKNN) - Báo cáo Thanh khoản thị trường và tiến độ triển khai hệ thống giao dịch mới KRX năm 2026</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_ssc_krx_operation_2025</t>
+        </is>
+      </c>
+      <c r="C18" s="3" t="inlineStr">
+        <is>
+          <t>Ủy ban Chứng khoán Nhà nước (UBCKNN) - Thông cáo chính thức đưa hệ thống công nghệ thông tin thị trường chứng khoán (KRX) vào vận hành từ ngày 05/05/2025</t>
+        </is>
+      </c>
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>https://ssc.gov.vn/webcenter/portal/ubck/pages_r/l/tintucsukien/</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2025-05-05</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:00:00+07:00</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>Phần thống kê giá trị giao dịch bình quân phiên (ADTV) đạt 22.000 tỷ VND</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t>Thông báo chính thức vận hành hệ thống KRX trên HOSE, HNX, VSDC ngày 05/05/2025 (S4)</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Đối chiếu văn bản chính thức vận hành hệ thống KRX từ 05/05/2025 (S4)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>SSI</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>ind_src_ftse_russell_reclassification_2026</t>
+        </is>
+      </c>
+      <c r="C19" s="3" t="inlineStr">
+        <is>
+          <t>FTSE Russell - Country Classification Annual Review FAQ v1.3 (Vietnam Secondary Emerging Market Effective Timeline)</t>
+        </is>
+      </c>
+      <c r="D19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.ftserussell.com/resources/country-classification</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-09T08:10:00+07:00</t>
+        </is>
+      </c>
+      <c r="G19" s="3" t="inlineStr">
+        <is>
+          <t>FAQ v1.3: Lộ trình phân loại thị trường mới nổi thứ cấp có hiệu lực từ 21/09/2026 triển khai theo các đợt (S5)</t>
+        </is>
+      </c>
+      <c r="H19" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>Tài liệu FAQ v1.3 FTSE Russell tháng 8/2026 (S5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>SSI</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
         <is>
           <t>ind_src_vietstock_sec_benchmark</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Vietstock Finance - Báo cáo Định giá &amp; Tỷ lệ dư nợ Margin toàn ngành Chứng khoán 2026</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C20" s="3" t="inlineStr">
+        <is>
+          <t>Vietstock Finance - Báo cáo Định giá &amp; Dư nợ Margin ngành Chứng khoán 2026</t>
+        </is>
+      </c>
+      <c r="D20" s="3" t="inlineStr">
         <is>
           <t>https://finance.vietstock.vn/nganh-nghe/8770/dich-vu-tai-chinh.htm</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>2026-09-30</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2026-10-09T08:15:00+07:00</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>Bảng P/B, P/E, Margin/VCSH các CTCK niêm yết</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>ĐÚNG</t>
+      <c r="G20" s="3" t="inlineStr">
+        <is>
+          <t>Bảng P/B, P/E, ROE và tỷ lệ dư nợ cho vay ký quỹ các CTCK niêm yết chốt phiên 30/09/2026</t>
+        </is>
+      </c>
+      <c r="H20" s="3" t="inlineStr">
+        <is>
+          <t>Nguoi_2</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>Dữ liệu giá chốt phiên 30/09/2026 và BCTC kiểm toán năm 2025</t>
         </is>
       </c>
     </row>
